--- a/files/hpp_produk.xlsx
+++ b/files/hpp_produk.xlsx
@@ -7945,7 +7945,7 @@
         <v>1242</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="L110">
         <v>8000</v>
@@ -9642,7 +9642,7 @@
         <v>1242</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="L159">
         <v>2000</v>
@@ -15249,7 +15249,7 @@
         <v>1249</v>
       </c>
       <c r="K321">
-        <v>4312.5</v>
+        <v>25872</v>
       </c>
       <c r="L321">
         <v>5500</v>
@@ -15771,7 +15771,7 @@
         <v>1249</v>
       </c>
       <c r="K336">
-        <v>4800</v>
+        <v>48000</v>
       </c>
       <c r="L336">
         <v>5000</v>
@@ -18953,7 +18953,7 @@
         <v>1249</v>
       </c>
       <c r="K427">
-        <v>8583.299999999999</v>
+        <v>85830</v>
       </c>
       <c r="L427">
         <v>9500</v>
@@ -19510,7 +19510,7 @@
         <v>1249</v>
       </c>
       <c r="K443">
-        <v>9300</v>
+        <v>111600</v>
       </c>
       <c r="L443">
         <v>11000</v>
@@ -26743,7 +26743,7 @@
         <v>1248</v>
       </c>
       <c r="K650">
-        <v>42960.3</v>
+        <v>1288800</v>
       </c>
       <c r="L650">
         <v>46000</v>

--- a/files/hpp_produk.xlsx
+++ b/files/hpp_produk.xlsx
@@ -16611,7 +16611,7 @@
         <v>1250</v>
       </c>
       <c r="K360">
-        <v>5250</v>
+        <v>525</v>
       </c>
       <c r="L360">
         <v>5250</v>

--- a/files/hpp_produk.xlsx
+++ b/files/hpp_produk.xlsx
@@ -15739,7 +15739,7 @@
         <v>1242</v>
       </c>
       <c r="K335">
-        <v>4800</v>
+        <v>4658</v>
       </c>
       <c r="L335">
         <v>6000</v>
@@ -15911,7 +15911,7 @@
         <v>1242</v>
       </c>
       <c r="K340">
-        <v>4900</v>
+        <v>4658</v>
       </c>
       <c r="L340">
         <v>6000</v>
@@ -15981,7 +15981,7 @@
         <v>1242</v>
       </c>
       <c r="K342">
-        <v>4900</v>
+        <v>4658</v>
       </c>
       <c r="L342">
         <v>6000</v>
@@ -16401,7 +16401,7 @@
         <v>1242</v>
       </c>
       <c r="K354">
-        <v>5000</v>
+        <v>4658</v>
       </c>
       <c r="L354">
         <v>6000</v>
